--- a/files/dataset-penjualan.xlsx
+++ b/files/dataset-penjualan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tudemaha/Documents/test-excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496E0383-68FE-C247-824C-9A6CD87629D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5921F16A-72B6-8B4A-AE0B-832E957CF7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{6E8E85D2-B145-3848-9EAA-97CE9C9B23EB}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{6E8E85D2-B145-3848-9EAA-97CE9C9B23EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Penjualan" sheetId="1" r:id="rId1"/>

--- a/files/dataset-penjualan.xlsx
+++ b/files/dataset-penjualan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tudemaha/Documents/test-excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5921F16A-72B6-8B4A-AE0B-832E957CF7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733095E2-6284-FC41-8DC0-D36FD4A7BAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{6E8E85D2-B145-3848-9EAA-97CE9C9B23EB}"/>
   </bookViews>
